--- a/backend/data/financials_by_company/1870.HK.xlsx
+++ b/backend/data/financials_by_company/1870.HK.xlsx
@@ -657,198 +657,204 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-151635</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.165</v>
+        <v>0.209801</v>
       </c>
       <c r="D2" t="n">
-        <v>15002000</v>
+        <v>27585000</v>
       </c>
       <c r="E2" t="n">
-        <v>-919000</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-919000</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>4441000</v>
+        <v>19107000</v>
       </c>
       <c r="H2" t="n">
-        <v>3050000</v>
+        <v>2941000</v>
       </c>
       <c r="I2" t="n">
-        <v>152542000</v>
+        <v>123014000</v>
       </c>
       <c r="J2" t="n">
-        <v>14083000</v>
+        <v>27585000</v>
       </c>
       <c r="K2" t="n">
-        <v>11033000</v>
+        <v>24644000</v>
       </c>
       <c r="L2" t="n">
-        <v>-3485000</v>
+        <v>-430000</v>
       </c>
       <c r="M2" t="n">
-        <v>3721000</v>
+        <v>464000</v>
       </c>
       <c r="N2" t="n">
-        <v>236000</v>
+        <v>34000</v>
       </c>
       <c r="O2" t="n">
-        <v>5208365</v>
+        <v>19107000</v>
       </c>
       <c r="P2" t="n">
-        <v>4441000</v>
+        <v>-187463000</v>
       </c>
       <c r="Q2" t="n">
-        <v>187845000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>138112000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
       <c r="S2" t="n">
-        <v>10797000</v>
+        <v>24610000</v>
       </c>
       <c r="T2" t="n">
-        <v>624000000</v>
+        <v>558181000</v>
       </c>
       <c r="U2" t="n">
-        <v>624000000</v>
+        <v>558181000</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0071</v>
+        <v>-0.3358</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0071</v>
+        <v>-0.3358</v>
       </c>
       <c r="X2" t="n">
-        <v>4441000</v>
+        <v>-187463000</v>
       </c>
       <c r="Y2" t="n">
-        <v>4441000</v>
+        <v>-187463000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>4441000</v>
+        <v>-187463000</v>
       </c>
       <c r="AB2" t="n">
-        <v>166000</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>4275000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
+        <v>-187463000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-206570000</v>
+      </c>
       <c r="AE2" t="n">
-        <v>4275000</v>
+        <v>19107000</v>
       </c>
       <c r="AF2" t="n">
-        <v>3037000</v>
+        <v>5073000</v>
       </c>
       <c r="AG2" t="n">
-        <v>7312000</v>
+        <v>24180000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-585000</v>
+        <v>2000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-919000</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>919000</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-3485000</v>
+        <v>-430000</v>
       </c>
       <c r="AL2" t="n">
-        <v>3721000</v>
+        <v>464000</v>
       </c>
       <c r="AM2" t="n">
-        <v>236000</v>
+        <v>34000</v>
       </c>
       <c r="AN2" t="n">
-        <v>12789000</v>
+        <v>24967000</v>
       </c>
       <c r="AO2" t="n">
-        <v>35303000</v>
+        <v>15098000</v>
       </c>
       <c r="AP2" t="n">
-        <v>35375000</v>
+        <v>15212000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>35375000</v>
+        <v>15212000</v>
       </c>
       <c r="AR2" t="n">
-        <v>48092000</v>
+        <v>40065000</v>
       </c>
       <c r="AS2" t="n">
-        <v>152542000</v>
+        <v>123014000</v>
       </c>
       <c r="AT2" t="n">
-        <v>200634000</v>
+        <v>163079000</v>
       </c>
       <c r="AU2" t="n">
-        <v>200634000</v>
+        <v>163079000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-274910.941476</v>
+        <v>-203147.484493</v>
       </c>
       <c r="C3" t="n">
-        <v>0.235369</v>
+        <v>0.266598</v>
       </c>
       <c r="D3" t="n">
-        <v>30641000</v>
+        <v>22843000</v>
       </c>
       <c r="E3" t="n">
-        <v>-1168000</v>
+        <v>-762000</v>
       </c>
       <c r="F3" t="n">
-        <v>-1168000</v>
+        <v>-762000</v>
       </c>
       <c r="G3" t="n">
-        <v>20046000</v>
+        <v>13009000</v>
       </c>
       <c r="H3" t="n">
-        <v>2282000</v>
+        <v>2267000</v>
       </c>
       <c r="I3" t="n">
-        <v>139614000</v>
+        <v>114625000</v>
       </c>
       <c r="J3" t="n">
-        <v>29473000</v>
+        <v>22081000</v>
       </c>
       <c r="K3" t="n">
-        <v>27191000</v>
+        <v>19814000</v>
       </c>
       <c r="L3" t="n">
-        <v>-2771000</v>
+        <v>-2358000</v>
       </c>
       <c r="M3" t="n">
-        <v>2825000</v>
+        <v>2402000</v>
       </c>
       <c r="N3" t="n">
-        <v>54000</v>
+        <v>44000</v>
       </c>
       <c r="O3" t="n">
-        <v>20939089.058524</v>
+        <v>13567852.515507</v>
       </c>
       <c r="P3" t="n">
-        <v>20046000</v>
+        <v>-79544000</v>
       </c>
       <c r="Q3" t="n">
-        <v>163878000</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>131357000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>102000</v>
+      </c>
       <c r="S3" t="n">
-        <v>27137000</v>
+        <v>19770000</v>
       </c>
       <c r="T3" t="n">
         <v>624000000</v>
@@ -857,139 +863,139 @@
         <v>624000000</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0321</v>
+        <v>-0.1275</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0321</v>
+        <v>-0.1275</v>
       </c>
       <c r="X3" t="n">
-        <v>20046000</v>
+        <v>-79544000</v>
       </c>
       <c r="Y3" t="n">
-        <v>20046000</v>
+        <v>-79544000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>20046000</v>
+        <v>-79544000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1415000</v>
+        <v>239000</v>
       </c>
       <c r="AC3" t="n">
-        <v>18631000</v>
+        <v>-79783000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-92553000</v>
       </c>
       <c r="AE3" t="n">
-        <v>18631000</v>
+        <v>12770000</v>
       </c>
       <c r="AF3" t="n">
-        <v>5735000</v>
+        <v>4642000</v>
       </c>
       <c r="AG3" t="n">
-        <v>24366000</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>17412000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-414000</v>
+      </c>
       <c r="AI3" t="n">
-        <v>-1168000</v>
+        <v>-762000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1168000</v>
+        <v>762000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-2771000</v>
+        <v>-2358000</v>
       </c>
       <c r="AL3" t="n">
-        <v>2825000</v>
+        <v>2402000</v>
       </c>
       <c r="AM3" t="n">
-        <v>54000</v>
+        <v>44000</v>
       </c>
       <c r="AN3" t="n">
-        <v>28524000</v>
+        <v>20858000</v>
       </c>
       <c r="AO3" t="n">
-        <v>24264000</v>
+        <v>16732000</v>
       </c>
       <c r="AP3" t="n">
-        <v>24267000</v>
+        <v>17702000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>24267000</v>
+        <v>17702000</v>
       </c>
       <c r="AR3" t="n">
-        <v>52788000</v>
+        <v>37590000</v>
       </c>
       <c r="AS3" t="n">
-        <v>139614000</v>
+        <v>114625000</v>
       </c>
       <c r="AT3" t="n">
-        <v>192402000</v>
+        <v>152215000</v>
       </c>
       <c r="AU3" t="n">
-        <v>192402000</v>
+        <v>152215000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-203147.484493</v>
+        <v>-274910.941476</v>
       </c>
       <c r="C4" t="n">
-        <v>0.266598</v>
+        <v>0.235369</v>
       </c>
       <c r="D4" t="n">
-        <v>22843000</v>
+        <v>30641000</v>
       </c>
       <c r="E4" t="n">
-        <v>-762000</v>
+        <v>-1168000</v>
       </c>
       <c r="F4" t="n">
-        <v>-762000</v>
+        <v>-1168000</v>
       </c>
       <c r="G4" t="n">
-        <v>13009000</v>
+        <v>20046000</v>
       </c>
       <c r="H4" t="n">
-        <v>2267000</v>
+        <v>2282000</v>
       </c>
       <c r="I4" t="n">
-        <v>114625000</v>
+        <v>139614000</v>
       </c>
       <c r="J4" t="n">
-        <v>22081000</v>
+        <v>29473000</v>
       </c>
       <c r="K4" t="n">
-        <v>19814000</v>
+        <v>27191000</v>
       </c>
       <c r="L4" t="n">
-        <v>-2358000</v>
+        <v>-2771000</v>
       </c>
       <c r="M4" t="n">
-        <v>2402000</v>
+        <v>2825000</v>
       </c>
       <c r="N4" t="n">
-        <v>44000</v>
+        <v>54000</v>
       </c>
       <c r="O4" t="n">
-        <v>13567852.515507</v>
+        <v>20939089.058524</v>
       </c>
       <c r="P4" t="n">
-        <v>-79544000</v>
+        <v>20046000</v>
       </c>
       <c r="Q4" t="n">
-        <v>131357000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>102000</v>
-      </c>
+        <v>163878000</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>19770000</v>
+        <v>27137000</v>
       </c>
       <c r="T4" t="n">
         <v>624000000</v>
@@ -998,225 +1004,219 @@
         <v>624000000</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1275</v>
+        <v>0.0321</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1275</v>
+        <v>0.0321</v>
       </c>
       <c r="X4" t="n">
-        <v>-79544000</v>
+        <v>20046000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-79544000</v>
+        <v>20046000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-79544000</v>
+        <v>20046000</v>
       </c>
       <c r="AB4" t="n">
-        <v>239000</v>
+        <v>1415000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-79783000</v>
+        <v>18631000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-92553000</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>12770000</v>
+        <v>18631000</v>
       </c>
       <c r="AF4" t="n">
-        <v>4642000</v>
+        <v>5735000</v>
       </c>
       <c r="AG4" t="n">
-        <v>17412000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-414000</v>
-      </c>
+        <v>24366000</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>-762000</v>
+        <v>-1168000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>762000</v>
+        <v>1168000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-2358000</v>
+        <v>-2771000</v>
       </c>
       <c r="AL4" t="n">
-        <v>2402000</v>
+        <v>2825000</v>
       </c>
       <c r="AM4" t="n">
-        <v>44000</v>
+        <v>54000</v>
       </c>
       <c r="AN4" t="n">
-        <v>20858000</v>
+        <v>28524000</v>
       </c>
       <c r="AO4" t="n">
-        <v>16732000</v>
+        <v>24264000</v>
       </c>
       <c r="AP4" t="n">
-        <v>17702000</v>
+        <v>24267000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17702000</v>
+        <v>24267000</v>
       </c>
       <c r="AR4" t="n">
-        <v>37590000</v>
+        <v>52788000</v>
       </c>
       <c r="AS4" t="n">
-        <v>114625000</v>
+        <v>139614000</v>
       </c>
       <c r="AT4" t="n">
-        <v>152215000</v>
+        <v>192402000</v>
       </c>
       <c r="AU4" t="n">
-        <v>152215000</v>
+        <v>192402000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-151635</v>
       </c>
       <c r="C5" t="n">
-        <v>0.209801</v>
+        <v>0.165</v>
       </c>
       <c r="D5" t="n">
-        <v>27585000</v>
+        <v>15002000</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-919000</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-919000</v>
       </c>
       <c r="G5" t="n">
-        <v>19107000</v>
+        <v>4441000</v>
       </c>
       <c r="H5" t="n">
-        <v>2941000</v>
+        <v>3050000</v>
       </c>
       <c r="I5" t="n">
-        <v>123014000</v>
+        <v>152542000</v>
       </c>
       <c r="J5" t="n">
-        <v>27585000</v>
+        <v>14083000</v>
       </c>
       <c r="K5" t="n">
-        <v>24644000</v>
+        <v>11033000</v>
       </c>
       <c r="L5" t="n">
-        <v>-430000</v>
+        <v>-3485000</v>
       </c>
       <c r="M5" t="n">
-        <v>464000</v>
+        <v>3721000</v>
       </c>
       <c r="N5" t="n">
-        <v>34000</v>
+        <v>236000</v>
       </c>
       <c r="O5" t="n">
-        <v>19107000</v>
+        <v>5208365</v>
       </c>
       <c r="P5" t="n">
-        <v>-187463000</v>
+        <v>4441000</v>
       </c>
       <c r="Q5" t="n">
-        <v>138112000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
+        <v>187845000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>24610000</v>
+        <v>10797000</v>
       </c>
       <c r="T5" t="n">
-        <v>558181000</v>
+        <v>624000000</v>
       </c>
       <c r="U5" t="n">
-        <v>558181000</v>
+        <v>624000000</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3358</v>
+        <v>0.0071</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3358</v>
+        <v>0.0071</v>
       </c>
       <c r="X5" t="n">
-        <v>-187463000</v>
+        <v>4441000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-187463000</v>
+        <v>4441000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-187463000</v>
+        <v>4441000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>166000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-187463000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-206570000</v>
-      </c>
+        <v>4275000</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>19107000</v>
+        <v>4275000</v>
       </c>
       <c r="AF5" t="n">
-        <v>5073000</v>
+        <v>3037000</v>
       </c>
       <c r="AG5" t="n">
-        <v>24180000</v>
+        <v>7312000</v>
       </c>
       <c r="AH5" t="n">
-        <v>2000</v>
+        <v>-585000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-919000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>919000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-430000</v>
+        <v>-3485000</v>
       </c>
       <c r="AL5" t="n">
-        <v>464000</v>
+        <v>3721000</v>
       </c>
       <c r="AM5" t="n">
-        <v>34000</v>
+        <v>236000</v>
       </c>
       <c r="AN5" t="n">
-        <v>24967000</v>
+        <v>12789000</v>
       </c>
       <c r="AO5" t="n">
-        <v>15098000</v>
+        <v>35303000</v>
       </c>
       <c r="AP5" t="n">
-        <v>15212000</v>
+        <v>35375000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15212000</v>
+        <v>35375000</v>
       </c>
       <c r="AR5" t="n">
-        <v>40065000</v>
+        <v>48092000</v>
       </c>
       <c r="AS5" t="n">
-        <v>123014000</v>
+        <v>152542000</v>
       </c>
       <c r="AT5" t="n">
-        <v>163079000</v>
+        <v>200634000</v>
       </c>
       <c r="AU5" t="n">
-        <v>163079000</v>
+        <v>200634000</v>
       </c>
     </row>
   </sheetData>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>624000000</v>
@@ -1566,44 +1566,42 @@
         <v>624000000</v>
       </c>
       <c r="D2" t="n">
-        <v>17285000</v>
+        <v>27006000</v>
       </c>
       <c r="E2" t="n">
-        <v>84944000</v>
+        <v>53809000</v>
       </c>
       <c r="F2" t="n">
-        <v>101616000</v>
+        <v>153557000</v>
       </c>
       <c r="G2" t="n">
-        <v>187823000</v>
+        <v>203537000</v>
       </c>
       <c r="H2" t="n">
-        <v>138118000</v>
+        <v>151702000</v>
       </c>
       <c r="I2" t="n">
-        <v>101616000</v>
+        <v>153557000</v>
       </c>
       <c r="J2" t="n">
-        <v>5209000</v>
+        <v>4509000</v>
       </c>
       <c r="K2" t="n">
-        <v>108088000</v>
+        <v>154237000</v>
       </c>
       <c r="L2" t="n">
-        <v>173546000</v>
+        <v>154237000</v>
       </c>
       <c r="M2" t="n">
-        <v>111273000</v>
+        <v>154237000</v>
       </c>
       <c r="N2" t="n">
-        <v>3185000</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>108088000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>118233000</v>
-      </c>
+        <v>154237000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
         <v>6240000</v>
       </c>
@@ -1611,144 +1609,138 @@
         <v>6240000</v>
       </c>
       <c r="S2" t="n">
-        <v>139898000</v>
+        <v>206958000</v>
       </c>
       <c r="T2" t="n">
-        <v>68992000</v>
+        <v>3532000</v>
       </c>
       <c r="U2" t="n">
-        <v>156000</v>
+        <v>18000</v>
       </c>
       <c r="V2" t="n">
-        <v>67922000</v>
+        <v>2262000</v>
       </c>
       <c r="W2" t="n">
-        <v>2464000</v>
+        <v>2262000</v>
       </c>
       <c r="X2" t="n">
-        <v>65458000</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>914000</v>
+        <v>1252000</v>
       </c>
       <c r="Z2" t="n">
-        <v>70906000</v>
+        <v>203426000</v>
       </c>
       <c r="AA2" t="n">
-        <v>17022000</v>
+        <v>51547000</v>
       </c>
       <c r="AB2" t="n">
-        <v>2745000</v>
+        <v>2247000</v>
       </c>
       <c r="AC2" t="n">
-        <v>14277000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
+        <v>49300000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>12397000</v>
+      </c>
       <c r="AE2" t="n">
-        <v>36504000</v>
+        <v>126486000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1769000</v>
+        <v>601000</v>
       </c>
       <c r="AG2" t="n">
-        <v>121000</v>
+        <v>1301000</v>
       </c>
       <c r="AH2" t="n">
-        <v>34614000</v>
+        <v>124584000</v>
       </c>
       <c r="AI2" t="n">
-        <v>251171000</v>
+        <v>361195000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>42147000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>2958000</v>
-      </c>
+        <v>6067000</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>701000</v>
+        <v>925000</v>
       </c>
       <c r="AM2" t="n">
-        <v>49000</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>6472000</v>
+        <v>680000</v>
       </c>
       <c r="AO2" t="n">
-        <v>390000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>6082000</v>
-      </c>
+        <v>680000</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>31967000</v>
+        <v>4462000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-4546000</v>
+        <v>-15803000</v>
       </c>
       <c r="AS2" t="n">
-        <v>36513000</v>
+        <v>20265000</v>
       </c>
       <c r="AT2" t="n">
-        <v>6454000</v>
+        <v>12305000</v>
       </c>
       <c r="AU2" t="n">
-        <v>5360000</v>
+        <v>5849000</v>
       </c>
       <c r="AV2" t="n">
-        <v>24699000</v>
+        <v>2111000</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>209024000</v>
+        <v>355128000</v>
       </c>
       <c r="AY2" t="n">
-        <v>5412000</v>
+        <v>73835000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6080000</v>
+        <v>10698000</v>
       </c>
       <c r="BA2" t="n">
-        <v>10751000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1649000</v>
-      </c>
+        <v>29571000</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
-        <v>9102000</v>
+        <v>29571000</v>
       </c>
       <c r="BE2" t="n">
-        <v>88590000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3114000</v>
-      </c>
+        <v>167337000</v>
+      </c>
+      <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="n">
-        <v>32627000</v>
+        <v>62091000</v>
       </c>
       <c r="BH2" t="n">
-        <v>-1027000</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>33654000</v>
+        <v>62091000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>62450000</v>
+        <v>22294000</v>
       </c>
       <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="n">
-        <v>62450000</v>
+        <v>22294000</v>
       </c>
       <c r="BM2" t="n">
-        <v>62450000</v>
+        <v>22294000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>624000000</v>
@@ -1757,44 +1749,42 @@
         <v>624000000</v>
       </c>
       <c r="D3" t="n">
-        <v>13438000</v>
+        <v>14446000</v>
       </c>
       <c r="E3" t="n">
-        <v>62046000</v>
+        <v>47984000</v>
       </c>
       <c r="F3" t="n">
-        <v>104742000</v>
+        <v>84677000</v>
       </c>
       <c r="G3" t="n">
-        <v>164449000</v>
+        <v>130326000</v>
       </c>
       <c r="H3" t="n">
-        <v>160436000</v>
+        <v>119163000</v>
       </c>
       <c r="I3" t="n">
-        <v>104742000</v>
+        <v>84677000</v>
       </c>
       <c r="J3" t="n">
-        <v>2339000</v>
+        <v>2335000</v>
       </c>
       <c r="K3" t="n">
-        <v>104742000</v>
+        <v>84677000</v>
       </c>
       <c r="L3" t="n">
-        <v>161036000</v>
+        <v>119666000</v>
       </c>
       <c r="M3" t="n">
-        <v>105762000</v>
+        <v>85167000</v>
       </c>
       <c r="N3" t="n">
-        <v>1020000</v>
+        <v>490000</v>
       </c>
       <c r="O3" t="n">
-        <v>104742000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>118233000</v>
-      </c>
+        <v>84677000</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
         <v>6240000</v>
       </c>
@@ -1802,63 +1792,63 @@
         <v>6240000</v>
       </c>
       <c r="S3" t="n">
-        <v>100154000</v>
+        <v>75582000</v>
       </c>
       <c r="T3" t="n">
-        <v>58163000</v>
+        <v>37039000</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="V3" t="n">
-        <v>57363000</v>
+        <v>36537000</v>
       </c>
       <c r="W3" t="n">
-        <v>1069000</v>
+        <v>1548000</v>
       </c>
       <c r="X3" t="n">
-        <v>56294000</v>
+        <v>34989000</v>
       </c>
       <c r="Y3" t="n">
-        <v>800000</v>
+        <v>484000</v>
       </c>
       <c r="Z3" t="n">
-        <v>41991000</v>
+        <v>38543000</v>
       </c>
       <c r="AA3" t="n">
-        <v>4683000</v>
+        <v>11447000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1270000</v>
+        <v>787000</v>
       </c>
       <c r="AC3" t="n">
-        <v>3413000</v>
+        <v>10660000</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>26821000</v>
+        <v>16565000</v>
       </c>
       <c r="AF3" t="n">
-        <v>630000</v>
+        <v>21000</v>
       </c>
       <c r="AG3" t="n">
-        <v>2465000</v>
+        <v>690000</v>
       </c>
       <c r="AH3" t="n">
-        <v>23726000</v>
+        <v>15854000</v>
       </c>
       <c r="AI3" t="n">
-        <v>205916000</v>
+        <v>160749000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3489000</v>
+        <v>3043000</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>395000</v>
+        <v>357000</v>
       </c>
       <c r="AM3" t="n">
-        <v>270000</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
@@ -1866,19 +1856,19 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>2824000</v>
+        <v>2686000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1651000</v>
+        <v>-591000</v>
       </c>
       <c r="AS3" t="n">
-        <v>4475000</v>
+        <v>3277000</v>
       </c>
       <c r="AT3" t="n">
-        <v>3184000</v>
+        <v>2326000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1291000</v>
+        <v>951000</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1887,55 +1877,55 @@
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>202427000</v>
+        <v>157706000</v>
       </c>
       <c r="AY3" t="n">
-        <v>15768000</v>
+        <v>15876000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3625000</v>
+        <v>4687000</v>
       </c>
       <c r="BA3" t="n">
-        <v>3437000</v>
+        <v>10954000</v>
       </c>
       <c r="BB3" t="n">
-        <v>17000</v>
+        <v>31000</v>
       </c>
       <c r="BC3" t="n">
-        <v>17000</v>
+        <v>31000</v>
       </c>
       <c r="BD3" t="n">
-        <v>3420000</v>
+        <v>10923000</v>
       </c>
       <c r="BE3" t="n">
-        <v>84061000</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
+        <v>64333000</v>
+      </c>
+      <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="n">
-        <v>49267000</v>
+        <v>28847000</v>
       </c>
       <c r="BH3" t="n">
-        <v>-967000</v>
+        <v>-459000</v>
       </c>
       <c r="BI3" t="n">
-        <v>50234000</v>
+        <v>29306000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>46269000</v>
-      </c>
-      <c r="BK3" t="inlineStr"/>
+        <v>33009000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1806000</v>
+      </c>
       <c r="BL3" t="n">
-        <v>46269000</v>
+        <v>31203000</v>
       </c>
       <c r="BM3" t="n">
-        <v>46269000</v>
+        <v>31203000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>624000000</v>
@@ -1944,42 +1934,44 @@
         <v>624000000</v>
       </c>
       <c r="D4" t="n">
-        <v>14446000</v>
+        <v>13438000</v>
       </c>
       <c r="E4" t="n">
-        <v>47984000</v>
+        <v>62046000</v>
       </c>
       <c r="F4" t="n">
-        <v>84677000</v>
+        <v>104742000</v>
       </c>
       <c r="G4" t="n">
-        <v>130326000</v>
+        <v>164449000</v>
       </c>
       <c r="H4" t="n">
-        <v>119163000</v>
+        <v>160436000</v>
       </c>
       <c r="I4" t="n">
-        <v>84677000</v>
+        <v>104742000</v>
       </c>
       <c r="J4" t="n">
-        <v>2335000</v>
+        <v>2339000</v>
       </c>
       <c r="K4" t="n">
-        <v>84677000</v>
+        <v>104742000</v>
       </c>
       <c r="L4" t="n">
-        <v>119666000</v>
+        <v>161036000</v>
       </c>
       <c r="M4" t="n">
-        <v>85167000</v>
+        <v>105762000</v>
       </c>
       <c r="N4" t="n">
-        <v>490000</v>
+        <v>1020000</v>
       </c>
       <c r="O4" t="n">
-        <v>84677000</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
+        <v>104742000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>118233000</v>
+      </c>
       <c r="Q4" t="n">
         <v>6240000</v>
       </c>
@@ -1987,63 +1979,63 @@
         <v>6240000</v>
       </c>
       <c r="S4" t="n">
-        <v>75582000</v>
+        <v>100154000</v>
       </c>
       <c r="T4" t="n">
-        <v>37039000</v>
+        <v>58163000</v>
       </c>
       <c r="U4" t="n">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>36537000</v>
+        <v>57363000</v>
       </c>
       <c r="W4" t="n">
-        <v>1548000</v>
+        <v>1069000</v>
       </c>
       <c r="X4" t="n">
-        <v>34989000</v>
+        <v>56294000</v>
       </c>
       <c r="Y4" t="n">
-        <v>484000</v>
+        <v>800000</v>
       </c>
       <c r="Z4" t="n">
-        <v>38543000</v>
+        <v>41991000</v>
       </c>
       <c r="AA4" t="n">
-        <v>11447000</v>
+        <v>4683000</v>
       </c>
       <c r="AB4" t="n">
-        <v>787000</v>
+        <v>1270000</v>
       </c>
       <c r="AC4" t="n">
-        <v>10660000</v>
+        <v>3413000</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>16565000</v>
+        <v>26821000</v>
       </c>
       <c r="AF4" t="n">
-        <v>21000</v>
+        <v>630000</v>
       </c>
       <c r="AG4" t="n">
-        <v>690000</v>
+        <v>2465000</v>
       </c>
       <c r="AH4" t="n">
-        <v>15854000</v>
+        <v>23726000</v>
       </c>
       <c r="AI4" t="n">
-        <v>160749000</v>
+        <v>205916000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3043000</v>
+        <v>3489000</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>357000</v>
+        <v>395000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>270000</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
@@ -2051,19 +2043,19 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>2686000</v>
+        <v>2824000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-591000</v>
+        <v>-1651000</v>
       </c>
       <c r="AS4" t="n">
-        <v>3277000</v>
+        <v>4475000</v>
       </c>
       <c r="AT4" t="n">
-        <v>2326000</v>
+        <v>3184000</v>
       </c>
       <c r="AU4" t="n">
-        <v>951000</v>
+        <v>1291000</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2072,55 +2064,55 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>157706000</v>
+        <v>202427000</v>
       </c>
       <c r="AY4" t="n">
-        <v>15876000</v>
+        <v>15768000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4687000</v>
+        <v>3625000</v>
       </c>
       <c r="BA4" t="n">
-        <v>10954000</v>
+        <v>3437000</v>
       </c>
       <c r="BB4" t="n">
-        <v>31000</v>
+        <v>17000</v>
       </c>
       <c r="BC4" t="n">
-        <v>31000</v>
+        <v>17000</v>
       </c>
       <c r="BD4" t="n">
-        <v>10923000</v>
+        <v>3420000</v>
       </c>
       <c r="BE4" t="n">
-        <v>64333000</v>
-      </c>
-      <c r="BF4" t="inlineStr"/>
+        <v>84061000</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
       <c r="BG4" t="n">
-        <v>28847000</v>
+        <v>49267000</v>
       </c>
       <c r="BH4" t="n">
-        <v>-459000</v>
+        <v>-967000</v>
       </c>
       <c r="BI4" t="n">
-        <v>29306000</v>
+        <v>50234000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>33009000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1806000</v>
-      </c>
+        <v>46269000</v>
+      </c>
+      <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="n">
-        <v>31203000</v>
+        <v>46269000</v>
       </c>
       <c r="BM4" t="n">
-        <v>31203000</v>
+        <v>46269000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>624000000</v>
@@ -2129,42 +2121,44 @@
         <v>624000000</v>
       </c>
       <c r="D5" t="n">
-        <v>27006000</v>
+        <v>17285000</v>
       </c>
       <c r="E5" t="n">
-        <v>53809000</v>
+        <v>84944000</v>
       </c>
       <c r="F5" t="n">
-        <v>153557000</v>
+        <v>101616000</v>
       </c>
       <c r="G5" t="n">
-        <v>203537000</v>
+        <v>187823000</v>
       </c>
       <c r="H5" t="n">
-        <v>151702000</v>
+        <v>138118000</v>
       </c>
       <c r="I5" t="n">
-        <v>153557000</v>
+        <v>101616000</v>
       </c>
       <c r="J5" t="n">
-        <v>4509000</v>
+        <v>5209000</v>
       </c>
       <c r="K5" t="n">
-        <v>154237000</v>
+        <v>108088000</v>
       </c>
       <c r="L5" t="n">
-        <v>154237000</v>
+        <v>173546000</v>
       </c>
       <c r="M5" t="n">
-        <v>154237000</v>
+        <v>111273000</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3185000</v>
       </c>
       <c r="O5" t="n">
-        <v>154237000</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>108088000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>118233000</v>
+      </c>
       <c r="Q5" t="n">
         <v>6240000</v>
       </c>
@@ -2172,133 +2166,139 @@
         <v>6240000</v>
       </c>
       <c r="S5" t="n">
-        <v>206958000</v>
+        <v>139898000</v>
       </c>
       <c r="T5" t="n">
-        <v>3532000</v>
+        <v>68992000</v>
       </c>
       <c r="U5" t="n">
-        <v>18000</v>
+        <v>156000</v>
       </c>
       <c r="V5" t="n">
-        <v>2262000</v>
+        <v>67922000</v>
       </c>
       <c r="W5" t="n">
-        <v>2262000</v>
+        <v>2464000</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>65458000</v>
       </c>
       <c r="Y5" t="n">
-        <v>1252000</v>
+        <v>914000</v>
       </c>
       <c r="Z5" t="n">
-        <v>203426000</v>
+        <v>70906000</v>
       </c>
       <c r="AA5" t="n">
-        <v>51547000</v>
+        <v>17022000</v>
       </c>
       <c r="AB5" t="n">
-        <v>2247000</v>
+        <v>2745000</v>
       </c>
       <c r="AC5" t="n">
-        <v>49300000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>12397000</v>
-      </c>
+        <v>14277000</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>126486000</v>
+        <v>36504000</v>
       </c>
       <c r="AF5" t="n">
-        <v>601000</v>
+        <v>1769000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1301000</v>
+        <v>121000</v>
       </c>
       <c r="AH5" t="n">
-        <v>124584000</v>
+        <v>34614000</v>
       </c>
       <c r="AI5" t="n">
-        <v>361195000</v>
+        <v>251171000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6067000</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
+        <v>42147000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2958000</v>
+      </c>
       <c r="AL5" t="n">
-        <v>925000</v>
+        <v>701000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="AN5" t="n">
-        <v>680000</v>
+        <v>6472000</v>
       </c>
       <c r="AO5" t="n">
-        <v>680000</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
+        <v>390000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>6082000</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>4462000</v>
+        <v>31967000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-15803000</v>
+        <v>-4546000</v>
       </c>
       <c r="AS5" t="n">
-        <v>20265000</v>
+        <v>36513000</v>
       </c>
       <c r="AT5" t="n">
-        <v>12305000</v>
+        <v>6454000</v>
       </c>
       <c r="AU5" t="n">
-        <v>5849000</v>
+        <v>5360000</v>
       </c>
       <c r="AV5" t="n">
-        <v>2111000</v>
+        <v>24699000</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>355128000</v>
+        <v>209024000</v>
       </c>
       <c r="AY5" t="n">
-        <v>73835000</v>
+        <v>5412000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10698000</v>
+        <v>6080000</v>
       </c>
       <c r="BA5" t="n">
-        <v>29571000</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
+        <v>10751000</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1649000</v>
+      </c>
       <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>29571000</v>
+        <v>9102000</v>
       </c>
       <c r="BE5" t="n">
-        <v>167337000</v>
-      </c>
-      <c r="BF5" t="inlineStr"/>
+        <v>88590000</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3114000</v>
+      </c>
       <c r="BG5" t="n">
-        <v>62091000</v>
+        <v>32627000</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>-1027000</v>
       </c>
       <c r="BI5" t="n">
-        <v>62091000</v>
+        <v>33654000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>22294000</v>
+        <v>62450000</v>
       </c>
       <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="n">
-        <v>22294000</v>
+        <v>62450000</v>
       </c>
       <c r="BM5" t="n">
-        <v>22294000</v>
+        <v>62450000</v>
       </c>
     </row>
   </sheetData>
@@ -2549,64 +2549,68 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-3655000</v>
+        <v>-70252000</v>
       </c>
       <c r="C2" t="n">
-        <v>-14100000</v>
+        <v>-63757000</v>
       </c>
       <c r="D2" t="n">
-        <v>34152000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>107558000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>19530000</v>
+      </c>
       <c r="F2" t="n">
-        <v>-26166000</v>
+        <v>-142000</v>
       </c>
       <c r="G2" t="n">
-        <v>62450000</v>
+        <v>22294000</v>
       </c>
       <c r="H2" t="n">
-        <v>46256000</v>
+        <v>42135000</v>
       </c>
       <c r="I2" t="n">
-        <v>-453000</v>
+        <v>-321000</v>
       </c>
       <c r="J2" t="n">
-        <v>16647000</v>
+        <v>-19520000</v>
       </c>
       <c r="K2" t="n">
-        <v>23875000</v>
+        <v>50654000</v>
       </c>
       <c r="L2" t="n">
-        <v>10779000</v>
+        <v>-8593000</v>
       </c>
       <c r="M2" t="n">
-        <v>-3721000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>-1970000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>19530000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>19530000</v>
+      </c>
       <c r="P2" t="n">
-        <v>20052000</v>
+        <v>43801000</v>
       </c>
       <c r="Q2" t="n">
-        <v>20052000</v>
+        <v>43801000</v>
       </c>
       <c r="R2" t="n">
-        <v>-14100000</v>
+        <v>-63757000</v>
       </c>
       <c r="S2" t="n">
-        <v>34152000</v>
+        <v>107558000</v>
       </c>
       <c r="T2" t="n">
-        <v>-29739000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-3600000</v>
-      </c>
+        <v>-64000</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>236000</v>
+        <v>78000</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -2614,394 +2618,400 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
-      <c r="Y2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
       <c r="Z2" t="n">
-        <v>-209000</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-209000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="n">
-        <v>-26166000</v>
+        <v>-142000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-26166000</v>
+        <v>-142000</v>
       </c>
       <c r="AF2" t="n">
-        <v>22511000</v>
+        <v>-70110000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-8300000</v>
+        <v>-4415000</v>
       </c>
       <c r="AH2" t="n">
-        <v>15800000</v>
+        <v>100414000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1095000</v>
+        <v>76833000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>10632000</v>
+        <v>-11811000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-3011000</v>
+        <v>11173000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-7287000</v>
+        <v>9079000</v>
       </c>
       <c r="AM2" t="n">
-        <v>16561000</v>
+        <v>9879000</v>
       </c>
       <c r="AN2" t="n">
-        <v>4127000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>1892000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>4316000</v>
+      </c>
       <c r="AP2" t="n">
-        <v>3050000</v>
+        <v>2941000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>21000</v>
+        <v>79000</v>
       </c>
       <c r="AR2" t="n">
-        <v>3029000</v>
+        <v>2862000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-397000</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
+        <v>438000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
       <c r="AU2" t="n">
-        <v>7312000</v>
+        <v>-175696000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1659000</v>
+        <v>-24531000</v>
       </c>
       <c r="C3" t="n">
-        <v>-13673000</v>
+        <v>-94085000</v>
       </c>
       <c r="D3" t="n">
-        <v>27734000</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>114388000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
       <c r="F3" t="n">
-        <v>-959000</v>
+        <v>-441000</v>
       </c>
       <c r="G3" t="n">
-        <v>46256000</v>
+        <v>31203000</v>
       </c>
       <c r="H3" t="n">
-        <v>31203000</v>
+        <v>22294000</v>
       </c>
       <c r="I3" t="n">
-        <v>181000</v>
+        <v>-439000</v>
       </c>
       <c r="J3" t="n">
-        <v>14872000</v>
+        <v>9348000</v>
       </c>
       <c r="K3" t="n">
-        <v>11353000</v>
+        <v>36173000</v>
       </c>
       <c r="L3" t="n">
-        <v>1575000</v>
+        <v>20137000</v>
       </c>
       <c r="M3" t="n">
-        <v>-2825000</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+        <v>-2286000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
       <c r="P3" t="n">
-        <v>14061000</v>
+        <v>20303000</v>
       </c>
       <c r="Q3" t="n">
-        <v>14061000</v>
+        <v>20303000</v>
       </c>
       <c r="R3" t="n">
-        <v>-13673000</v>
+        <v>-94085000</v>
       </c>
       <c r="S3" t="n">
-        <v>27734000</v>
+        <v>114388000</v>
       </c>
       <c r="T3" t="n">
-        <v>901000</v>
+        <v>-2735000</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>54000</v>
+        <v>133000</v>
       </c>
       <c r="W3" t="n">
-        <v>1806000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1806000</v>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+        <v>-1806000</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="n">
+        <v>-1806000</v>
+      </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-621000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-621000</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>-959000</v>
+        <v>-441000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-959000</v>
+        <v>-441000</v>
       </c>
       <c r="AF3" t="n">
-        <v>2618000</v>
+        <v>-24090000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-4248000</v>
+        <v>-5254000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-23537000</v>
+        <v>26783000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-20071000</v>
+        <v>50013000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8722000</v>
+        <v>-40882000</v>
       </c>
       <c r="AK3" t="n">
-        <v>907000</v>
+        <v>908000</v>
       </c>
       <c r="AL3" t="n">
-        <v>7517000</v>
+        <v>18618000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-20928000</v>
+        <v>4688000</v>
       </c>
       <c r="AN3" t="n">
-        <v>2771000</v>
+        <v>4191000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>9985000</v>
       </c>
       <c r="AP3" t="n">
-        <v>2282000</v>
+        <v>2267000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="AR3" t="n">
-        <v>2282000</v>
+        <v>2195000</v>
       </c>
       <c r="AS3" t="n">
-        <v>-184000</v>
+        <v>-487000</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>4957000</v>
       </c>
       <c r="AU3" t="n">
-        <v>24366000</v>
+        <v>-75141000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-24531000</v>
+        <v>1659000</v>
       </c>
       <c r="C4" t="n">
-        <v>-94085000</v>
+        <v>-13673000</v>
       </c>
       <c r="D4" t="n">
-        <v>114388000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
+        <v>27734000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-441000</v>
+        <v>-959000</v>
       </c>
       <c r="G4" t="n">
+        <v>46256000</v>
+      </c>
+      <c r="H4" t="n">
         <v>31203000</v>
       </c>
-      <c r="H4" t="n">
-        <v>22294000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-439000</v>
+        <v>181000</v>
       </c>
       <c r="J4" t="n">
-        <v>9348000</v>
+        <v>14872000</v>
       </c>
       <c r="K4" t="n">
-        <v>36173000</v>
+        <v>11353000</v>
       </c>
       <c r="L4" t="n">
-        <v>20137000</v>
+        <v>1575000</v>
       </c>
       <c r="M4" t="n">
-        <v>-2286000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
+        <v>-2825000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>20303000</v>
+        <v>14061000</v>
       </c>
       <c r="Q4" t="n">
-        <v>20303000</v>
+        <v>14061000</v>
       </c>
       <c r="R4" t="n">
-        <v>-94085000</v>
+        <v>-13673000</v>
       </c>
       <c r="S4" t="n">
-        <v>114388000</v>
+        <v>27734000</v>
       </c>
       <c r="T4" t="n">
-        <v>-2735000</v>
+        <v>901000</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>133000</v>
+        <v>54000</v>
       </c>
       <c r="W4" t="n">
-        <v>-1806000</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="n">
-        <v>-1806000</v>
-      </c>
+        <v>1806000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1806000</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>-621000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-621000</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>-441000</v>
+        <v>-959000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-441000</v>
+        <v>-959000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-24090000</v>
+        <v>2618000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-5254000</v>
+        <v>-4248000</v>
       </c>
       <c r="AH4" t="n">
-        <v>26783000</v>
+        <v>-23537000</v>
       </c>
       <c r="AI4" t="n">
-        <v>50013000</v>
+        <v>-20071000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-40882000</v>
+        <v>8722000</v>
       </c>
       <c r="AK4" t="n">
-        <v>908000</v>
+        <v>907000</v>
       </c>
       <c r="AL4" t="n">
-        <v>18618000</v>
+        <v>7517000</v>
       </c>
       <c r="AM4" t="n">
-        <v>4688000</v>
+        <v>-20928000</v>
       </c>
       <c r="AN4" t="n">
-        <v>4191000</v>
+        <v>2771000</v>
       </c>
       <c r="AO4" t="n">
-        <v>9985000</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2267000</v>
+        <v>2282000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>72000</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>2195000</v>
+        <v>2282000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-487000</v>
+        <v>-184000</v>
       </c>
       <c r="AT4" t="n">
-        <v>4957000</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>-75141000</v>
+        <v>24366000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-70252000</v>
+        <v>-3655000</v>
       </c>
       <c r="C5" t="n">
-        <v>-63757000</v>
+        <v>-14100000</v>
       </c>
       <c r="D5" t="n">
-        <v>107558000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>19530000</v>
-      </c>
+        <v>34152000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>-142000</v>
+        <v>-26166000</v>
       </c>
       <c r="G5" t="n">
-        <v>22294000</v>
+        <v>62450000</v>
       </c>
       <c r="H5" t="n">
-        <v>42135000</v>
+        <v>46256000</v>
       </c>
       <c r="I5" t="n">
-        <v>-321000</v>
+        <v>-453000</v>
       </c>
       <c r="J5" t="n">
-        <v>-19520000</v>
+        <v>16647000</v>
       </c>
       <c r="K5" t="n">
-        <v>50654000</v>
+        <v>23875000</v>
       </c>
       <c r="L5" t="n">
-        <v>-8593000</v>
+        <v>10779000</v>
       </c>
       <c r="M5" t="n">
-        <v>-1970000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>19530000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>19530000</v>
-      </c>
+        <v>-3721000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>43801000</v>
+        <v>20052000</v>
       </c>
       <c r="Q5" t="n">
-        <v>43801000</v>
+        <v>20052000</v>
       </c>
       <c r="R5" t="n">
-        <v>-63757000</v>
+        <v>-14100000</v>
       </c>
       <c r="S5" t="n">
-        <v>107558000</v>
+        <v>34152000</v>
       </c>
       <c r="T5" t="n">
-        <v>-64000</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>-29739000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-3600000</v>
+      </c>
       <c r="V5" t="n">
-        <v>78000</v>
+        <v>236000</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -3009,74 +3019,64 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-209000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
+        <v>-209000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>-142000</v>
+        <v>-26166000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-142000</v>
+        <v>-26166000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-70110000</v>
+        <v>22511000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-4415000</v>
+        <v>-8300000</v>
       </c>
       <c r="AH5" t="n">
-        <v>100414000</v>
+        <v>15800000</v>
       </c>
       <c r="AI5" t="n">
-        <v>76833000</v>
+        <v>-1095000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-11811000</v>
+        <v>10632000</v>
       </c>
       <c r="AK5" t="n">
-        <v>11173000</v>
+        <v>-3011000</v>
       </c>
       <c r="AL5" t="n">
-        <v>9079000</v>
+        <v>-7287000</v>
       </c>
       <c r="AM5" t="n">
-        <v>9879000</v>
+        <v>16561000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1892000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>4316000</v>
-      </c>
+        <v>4127000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>2941000</v>
+        <v>3050000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>79000</v>
+        <v>21000</v>
       </c>
       <c r="AR5" t="n">
-        <v>2862000</v>
+        <v>3029000</v>
       </c>
       <c r="AS5" t="n">
-        <v>438000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
+        <v>-397000</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>-175696000</v>
+        <v>7312000</v>
       </c>
     </row>
   </sheetData>
@@ -3601,187 +3601,187 @@
       </c>
       <c r="CX1" t="inlineStr">
         <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="EI1" t="inlineStr">
@@ -3889,28 +3889,28 @@
         <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="n">
-        <v>0.48</v>
+        <v>0.405</v>
       </c>
       <c r="X2" t="n">
-        <v>0.47</v>
+        <v>0.35</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.485</v>
+        <v>0.405</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.48</v>
+        <v>0.405</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.47</v>
+        <v>0.35</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.485</v>
+        <v>0.405</v>
       </c>
       <c r="AD2" t="n">
         <v>1591056000</v>
@@ -3919,34 +3919,34 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.826</v>
       </c>
       <c r="AG2" t="n">
-        <v>4410000</v>
+        <v>1655000</v>
       </c>
       <c r="AH2" t="n">
-        <v>4410000</v>
+        <v>1655000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1853000</v>
+        <v>1696016</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1945750</v>
+        <v>963250</v>
       </c>
       <c r="AK2" t="n">
-        <v>1945750</v>
+        <v>963250</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.455</v>
+        <v>0.36</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.49</v>
+        <v>0.38</v>
       </c>
       <c r="AN2" t="n">
-        <v>478069888</v>
+        <v>386524576</v>
       </c>
       <c r="AO2" t="n">
-        <v>488241600</v>
+        <v>386524600</v>
       </c>
       <c r="AP2" t="n">
         <v>0.164</v>
@@ -3961,13 +3961,13 @@
         <v>0.105</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.227672</v>
+        <v>2.6096072</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.4633</v>
+        <v>0.4705</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.43684</v>
+        <v>0.446975</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>460164608</v>
+        <v>358447616</v>
       </c>
       <c r="BB2" t="n">
         <v>-0.33167</v>
@@ -4008,7 +4008,7 @@
         <v>0.133</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.5338345</v>
+        <v>2.8571427</v>
       </c>
       <c r="BJ2" t="n">
         <v>1767139200</v>
@@ -4026,16 +4026,16 @@
         <v>-0.06</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.107</v>
+        <v>2.42</v>
       </c>
       <c r="BP2" t="n">
-        <v>-9.515000000000001</v>
+        <v>-7.412</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1</v>
+        <v>0.7391304</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BS2" t="n">
         <v>0.01</v>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="BV2" t="n">
-        <v>0.47</v>
+        <v>0.38</v>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
@@ -4148,140 +4148,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="CY2" t="n">
-        <v>-2.0833313</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="CX2" t="n">
+        <v>-0.02000001</v>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>0.35 - 0.405</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DA2" t="n">
+        <v>1696016</v>
       </c>
       <c r="DB2" t="n">
-        <v>1780301306</v>
+        <v>0.21599999</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0.00999999</v>
+        <v>1.3170731</v>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>0.47 - 0.485</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
+          <t>0.164 - 0.65</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>-0.26999998</v>
       </c>
       <c r="DF2" t="n">
-        <v>1853000</v>
+        <v>-0.4153846</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.306</v>
+        <v>73.91304</v>
       </c>
       <c r="DH2" t="n">
-        <v>1.8658535</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>0.164 - 0.65</t>
-        </is>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-0.17999998</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>-0.27692306</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>100</v>
+        <v>1743081213</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>1743081213</v>
+      </c>
+      <c r="DJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="b">
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>1743081213</v>
+        <v>1573176600000</v>
       </c>
       <c r="DN2" t="n">
-        <v>1743081213</v>
-      </c>
-      <c r="DO2" t="b">
-        <v>0</v>
+        <v>-5.0000024</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.38</v>
       </c>
       <c r="DP2" t="n">
         <v>-0.06</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.006700009</v>
+        <v>-0.0905</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.014461492</v>
+        <v>-0.19234857</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.03316</v>
+        <v>-0.06697500000000001</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.0759088</v>
-      </c>
-      <c r="DU2" t="b">
-        <v>0</v>
+        <v>-0.1498406</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>15</v>
       </c>
       <c r="DV2" t="n">
-        <v>1573176600000</v>
+        <v>15</v>
       </c>
       <c r="DW2" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DX2" t="n">
+        <v>1782115693</v>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>finmb_639857824</t>
         </is>
       </c>
-      <c r="DY2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DZ2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="EA2" t="n">
+      <c r="EC2" t="n">
         <v>28800000</v>
       </c>
-      <c r="EB2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="EC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="inlineStr">
+      <c r="EE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="inlineStr">
         <is>
           <t>ACME INTL HLDGS</t>
         </is>
       </c>
-      <c r="EE2" t="inlineStr">
+      <c r="EG2" t="inlineStr">
         <is>
           <t>Acme International Holdings Limited</t>
         </is>
       </c>
-      <c r="EF2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
       </c>
       <c r="EI2" t="inlineStr"/>
     </row>
